--- a/themes/cardsConsultation.xlsx
+++ b/themes/cardsConsultation.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -470,116 +470,116 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98</v>
+        <v>179</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Информацию по карте *{{$session.chosenCard.pan}} вы можете получить по [ссылке]({{$temp.debitCardConditionsLink}})</t>
+          <t xml:space="preserve">    1.	Выберите кредитную карту - «Подробнее об условиях»</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Информацию по карте *{{$session.chosenCard.pan}} вы можете получить по [ссылке]({{$temp.debitCardConditionsLink}}).</t>
+          <t xml:space="preserve">    1.	Выберите кредитную карту — «Подробнее об условиях»</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>дефис заменён на тире</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110</v>
+        <v>201</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Информацию о потраченной сумме, которая вошла в оборот дебетовой карты *{{$session.chosenCard.pan}} по «Уралсиб Бонус», вы можете уточнить по [ссылке]({{$temp.debitCardProfitBonusLink}})</t>
+          <t xml:space="preserve">      • Сумма - {{$temp.rubleFormMinSum}} </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Информацию о потраченной сумме, которая вошла в оборот дебетовой карты *{{$session.chosenCard.pan}} по «Уралсиб Бонус», вы можете уточнить по [ссылке]({{$temp.debitCardProfitBonusLink}}).</t>
+          <t xml:space="preserve">      • Сумма — {{$temp.rubleFormMinSum}} </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>дефис заменён на тире</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122</v>
+        <v>299</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Информацию о сумме начисленных процентов по карте *{{$session.chosenCard.pan}} вы можете уточнить по [ссылке]({{$temp.debitCardProfitPercentLink}})</t>
+          <t xml:space="preserve">    - "Если вы забыли PIN-код и опция смены отсутствует, нужно перевыпустить карту: самостоятельно в «Уралсиб Онлайн» или в отделении банка в пределах филиала обслуживания."</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Информацию о сумме начисленных процентов по карте *{{$session.chosenCard.pan}} вы можете уточнить по [ссылке]({{$temp.debitCardProfitPercentLink}}).</t>
+          <t xml:space="preserve">    - "Если вы забыли ПИН-код и опция смены отсутствует, нужно перевыпустить карту: самостоятельно в «Уралсиб Онлайн» или в отделении банка в пределах филиала обслуживания."</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>«PIN-код» приведено к «ПИН-код» — для единообразия с остальной базой (используется кириллица)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130</v>
+        <v>352</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Информацию о ставке по карте *{{$session.chosenCard.pan}} вы можете уточнить по [ссылке]({{$temp.debitCardProfitRateLink}})</t>
+          <t xml:space="preserve">      • Дебетовая карта - до 10 рабочих дней</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Информацию о ставке по карте *{{$session.chosenCard.pan}} вы можете уточнить по [ссылке]({{$temp.debitCardProfitRateLink}}).</t>
+          <t xml:space="preserve">      • Дебетовая карта — до 10 рабочих дней</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>дефис заменён на тире</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>175</v>
+        <v>353</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Информацию по карте *{{$session.chosenCard.pan}} вы можете получить по [ссылке]({{$temp.creditCardConditionsLink}})</t>
+          <t xml:space="preserve">      • Кредитная карта - до 14 рабочих дней</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Информацию по карте *{{$session.chosenCard.pan}} вы можете получить по [ссылке]({{$temp.creditCardConditionsLink}}).</t>
+          <t xml:space="preserve">      • Кредитная карта — до 14 рабочих дней</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>дефис заменён на тире</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>179</v>
+        <v>359</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1.	Выберите кредитную карту - «Подробнее об условиях»</t>
+          <t xml:space="preserve">      3. Нажмите кнопку «Перевыпустить», заполните поля - «Отправить заявку».</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1.	Выберите кредитную карту — «Подробнее об условиях»</t>
+          <t xml:space="preserve">      3. Нажмите кнопку «Перевыпустить», заполните поля — «Отправить заявку».</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -590,16 +590,16 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>201</v>
+        <v>362</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">      • Сумма - {{$temp.rubleFormMinSum}} </t>
+          <t xml:space="preserve">      • Дебетовая карта - до 10 рабочих дней</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">      • Сумма — {{$temp.rubleFormMinSum}} </t>
+          <t xml:space="preserve">      • Дебетовая карта — до 10 рабочих дней</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -610,299 +610,79 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>231</v>
+        <v>363</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  {{$session.name}}, ваша карта *{{$session.chosenCard.pan}} успешно заблокирована. Рекомендую также заблокировать ваш личный кабинет, чтобы обезопасить денежные средства. Произвести блокировку личного кабинета вы можете по [ссылке]({{$temp.cardBlockLKLink}})</t>
+          <t xml:space="preserve">      • Кредитная карта - до 14 рабочих дней</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  {{$session.name}}, ваша карта *{{$session.chosenCard.pan}} успешно заблокирована. Рекомендую также заблокировать ваш личный кабинет, чтобы обезопасить денежные средства. Произвести блокировку личного кабинета вы можете по [ссылке]({{$temp.cardBlockLKLink}}).</t>
+          <t xml:space="preserve">      • Кредитная карта — до 14 рабочих дней</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>дефис заменён на тире</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>253</v>
+        <v>368</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    {{$session.name}}, разблокировать карту можно в отделении банка или по [ссылке]({{$temp.cardUnblockLink}})</t>
+          <t xml:space="preserve">    2. Оплачивать товары и услуги по куар-коду с помощью мобильного приложения на смартфоне. </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    {{$session.name}}, разблокировать карту можно в отделении банка или по [ссылке]({{$temp.cardUnblockLink}}).</t>
+          <t xml:space="preserve">    2. Оплачивать товары и услуги по QR-коду с помощью мобильного приложения на смартфоне. </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>«куар-коду» приведено к «QR-коду» — для единообразия с остальной базой</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>292</v>
+        <v>418</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  HasPinsetAndVerified: Для установки ПИН-кода перейдите по [ссылке]({{$temp.cardPINInstallLink}})</t>
+          <t xml:space="preserve">    reply: Чтобы активировать карту установите ПИН-код. Для активации бесконтактной оплаты по карте совершите покупку с вводом установленного PIN-кода или запросите баланс в банкомате Уралсиба.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  HasPinsetAndVerified: Для установки ПИН-кода перейдите по [ссылке]({{$temp.cardPINInstallLink}}).</t>
+          <t xml:space="preserve">    reply: Чтобы активировать карту, установите ПИН-код. Для активации бесконтактной оплаты по карте совершите покупку с вводом установленного ПИН-кода или запросите баланс в банкомате Уралсиба.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>добавлена запятая после придаточного «Чтобы активировать карту»; «PIN-кода» приведено к «ПИН-кода» для единообразия в пределах предложения</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>299</v>
+        <v>442</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - "Если вы забыли PIN-код и опция смены отсутствует, нужно перевыпустить карту: самостоятельно в «Уралсиб Онлайн» или в отделении банка в пределах филиала обслуживания."</t>
+          <t xml:space="preserve">       Чтобы убрать карту из стоп-листа, нужно определить транспортную компанию, у которой не прошла оплата. В каждом регионе свой оператор - проверить можно здесь: https://bilet.nspk.ru/ </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - "Если вы забыли ПИН-код и опция смены отсутствует, нужно перевыпустить карту: самостоятельно в «Уралсиб Онлайн» или в отделении банка в пределах филиала обслуживания."</t>
+          <t xml:space="preserve">       Чтобы убрать карту из стоп-листа, нужно определить транспортную компанию, у которой не прошла оплата. В каждом регионе свой оператор — проверить можно здесь: https://bilet.nspk.ru/ </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
-        <is>
-          <t>«PIN-код» приведено к «ПИН-код» — для единообразия с остальной базой (используется кириллица)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>352</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Дебетовая карта - до 10 рабочих дней</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Дебетовая карта — до 10 рабочих дней</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>дефис заменён на тире</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>353</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Кредитная карта - до 14 рабочих дней</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Кредитная карта — до 14 рабочих дней</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>дефис заменён на тире</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>359</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      3. Нажмите кнопку «Перевыпустить», заполните поля - «Отправить заявку».</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      3. Нажмите кнопку «Перевыпустить», заполните поля — «Отправить заявку».</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>дефис заменён на тире</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>362</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Дебетовая карта - до 10 рабочих дней</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Дебетовая карта — до 10 рабочих дней</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>дефис заменён на тире</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>363</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Кредитная карта - до 14 рабочих дней</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Кредитная карта — до 14 рабочих дней</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>дефис заменён на тире</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>368</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    2. Оплачивать товары и услуги по куар-коду с помощью мобильного приложения на смартфоне. </t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    2. Оплачивать товары и услуги по QR-коду с помощью мобильного приложения на смартфоне. </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>«куар-коду» приведено к «QR-коду» — для единообразия с остальной базой</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>373</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Выпустить цифровую карту можно в приложении «Уралсиб Онлайн» или в веб-версии на [сайте](https://online.uralsib.ru/)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Выпустить цифровую карту можно в приложении «Уралсиб Онлайн» или в веб-версии на [сайте](https://online.uralsib.ru/).</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>415</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         Карта отделений банка доступна [здесь]({{$temp.officeLink}})</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         Карта отделений банка доступна [здесь]({{$temp.officeLink}}).</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>418</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    reply: Чтобы активировать карту установите ПИН-код. Для активации бесконтактной оплаты по карте совершите покупку с вводом установленного PIN-кода или запросите баланс в банкомате Уралсиба.</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    reply: Чтобы активировать карту, установите ПИН-код. Для активации бесконтактной оплаты по карте совершите покупку с вводом установленного ПИН-кода или запросите баланс в банкомате Уралсиба.</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>добавлена запятая после придаточного «Чтобы активировать карту»; «PIN-кода» приведено к «ПИН-кода» для единообразия в пределах предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>435</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        - Для уточнения возможности закрытия заявки на перевыпуск карты напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        - Для уточнения возможности закрытия заявки на перевыпуск карты напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/).</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>442</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       Чтобы убрать карту из стоп-листа, нужно определить транспортную компанию, у которой не прошла оплата. В каждом регионе свой оператор - проверить можно здесь: https://bilet.nspk.ru/ </t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       Чтобы убрать карту из стоп-листа, нужно определить транспортную компанию, у которой не прошла оплата. В каждом регионе свой оператор — проверить можно здесь: https://bilet.nspk.ru/ </t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
         <is>
           <t>дефис заменён на тире</t>
         </is>
